--- a/test-results/excel-reports/stage_report_2026-05-13.xlsx
+++ b/test-results/excel-reports/stage_report_2026-05-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="66">
   <si>
     <t>No.</t>
   </si>
@@ -63,7 +63,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>16.27</t>
+    <t>15.48</t>
   </si>
   <si>
     <t>tests/ui/keyboardAccessibilityTest.stage.spec.ts</t>
@@ -72,7 +72,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-05-13T06:22:02.525Z</t>
+    <t>2026-05-13T06:26:10.687Z</t>
   </si>
   <si>
     <t>STAGE</t>
@@ -81,43 +81,52 @@
     <t>Test 2: Landing Page Keyboard Navigation</t>
   </si>
   <si>
-    <t>0.03</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:22:02.569Z</t>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>2026-05-13T06:26:10.744Z</t>
   </si>
   <si>
     <t>Test 3: Signature Module Keyboard Navigation</t>
   </si>
   <si>
-    <t>17.58</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:22:20.170Z</t>
+    <t>17.17</t>
+  </si>
+  <si>
+    <t>2026-05-13T06:26:27.930Z</t>
   </si>
   <si>
     <t>Test 4: Upload Document via Keyboard</t>
   </si>
   <si>
+    <t>24.34</t>
+  </si>
+  <si>
+    <t>2026-05-13T06:26:52.284Z</t>
+  </si>
+  <si>
+    <t>Test 5: Signature Advance Workflow via Keyboard</t>
+  </si>
+  <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>18.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
+    <t>14.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: locator.waitFor: Target page, context or browser has been closed
 Call log:
-[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
-TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
+[2m  - waiting for locator('text="Add Recipients"') to be visible[22m
+Error: locator.waitFor: Target page, context or browser has been closed
 Call log:
-[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
-    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:188:52</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:22:38.427Z</t>
-  </si>
-  <si>
-    <t>Test 5: Signature Advance Workflow via Keyboard</t>
+[2m  - waiting for locator('text="Add Recipients"') to be visible[22m
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:270:52</t>
+  </si>
+  <si>
+    <t>2026-05-13T06:27:06.347Z</t>
+  </si>
+  <si>
+    <t>Test 6: Sign A Document via Keyboard</t>
   </si>
   <si>
     <t>SKIPPED</t>
@@ -126,18 +135,21 @@
     <t>0.00</t>
   </si>
   <si>
-    <t>Test 6: Sign A Document via Keyboard</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:22:38.428Z</t>
+    <t>2026-05-13T06:27:06.348Z</t>
   </si>
   <si>
     <t>Test 7: Menu and Dropdown Keyboard Navigation</t>
   </si>
   <si>
+    <t>2026-05-13T06:27:06.349Z</t>
+  </si>
+  <si>
     <t>Test 8: Combined Keyboard Workflow</t>
   </si>
   <si>
+    <t>2026-05-13T06:27:06.350Z</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -150,7 +162,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>5/13/2026, 12:22:38 PM</t>
+    <t>5/13/2026, 12:27:06 PM</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -162,43 +174,43 @@
     <t>Passed</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Timed Out</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Timed Out</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Pass Rate</t>
   </si>
   <si>
-    <t>37.50%</t>
+    <t>50.00%</t>
   </si>
   <si>
     <t>Total Duration (s)</t>
   </si>
   <si>
-    <t>52.11</t>
+    <t>71.06</t>
   </si>
   <si>
     <t>Avg Duration (ms)</t>
   </si>
   <si>
-    <t>6513.50</t>
+    <t>8882.25</t>
   </si>
   <si>
     <t>failed</t>
@@ -737,7 +749,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>16271</v>
+        <v>15483</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>
@@ -778,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>22</v>
@@ -819,7 +831,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="2">
-        <v>17584</v>
+        <v>17168</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>25</v>
@@ -856,14 +868,14 @@
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2">
+        <v>24337</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="E5" s="2">
-        <v>18223</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>17</v>
@@ -872,7 +884,7 @@
         <v>161</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J5" s="2">
         <v>0</v>
@@ -881,7 +893,7 @@
         <v>18</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>20</v>
@@ -892,28 +904,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>33</v>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
+        <v>14028</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
@@ -922,7 +934,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>20</v>
@@ -939,19 +951,19 @@
         <v>14</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>18</v>
@@ -963,7 +975,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>20</v>
@@ -974,25 +986,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>18</v>
@@ -1004,7 +1016,7 @@
         <v>18</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>20</v>
@@ -1015,25 +1027,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>18</v>
@@ -1045,7 +1057,7 @@
         <v>18</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>20</v>
@@ -1072,10 +1084,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1088,18 +1100,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1112,42 +1124,42 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1160,26 +1172,26 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1187,7 +1199,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1249,7 @@
         <v>9</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1245,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>14</v>
@@ -1254,16 +1266,16 @@
         <v>17</v>
       </c>
       <c r="E2" s="11">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="F2" s="11">
-        <v>18223</v>
+        <v>14028</v>
       </c>
       <c r="G2" s="11">
         <v>0</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/test-results/excel-reports/stage_report_2026-05-13.xlsx
+++ b/test-results/excel-reports/stage_report_2026-05-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="67">
   <si>
     <t>No.</t>
   </si>
@@ -63,7 +63,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>15.48</t>
+    <t>14.97</t>
   </si>
   <si>
     <t>tests/ui/keyboardAccessibilityTest.stage.spec.ts</t>
@@ -72,7 +72,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-05-13T06:26:10.687Z</t>
+    <t>2026-05-13T07:28:39.735Z</t>
   </si>
   <si>
     <t>STAGE</t>
@@ -81,52 +81,61 @@
     <t>Test 2: Landing Page Keyboard Navigation</t>
   </si>
   <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:26:10.744Z</t>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>2026-05-13T07:28:39.825Z</t>
   </si>
   <si>
     <t>Test 3: Signature Module Keyboard Navigation</t>
   </si>
   <si>
-    <t>17.17</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:26:27.930Z</t>
+    <t>17.40</t>
+  </si>
+  <si>
+    <t>2026-05-13T07:28:57.249Z</t>
   </si>
   <si>
     <t>Test 4: Upload Document via Keyboard</t>
   </si>
   <si>
-    <t>24.34</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:26:52.284Z</t>
+    <t>30.40</t>
+  </si>
+  <si>
+    <t>2026-05-13T07:29:27.679Z</t>
   </si>
   <si>
     <t>Test 5: Signature Advance Workflow via Keyboard</t>
   </si>
   <si>
+    <t>3.20</t>
+  </si>
+  <si>
+    <t>2026-05-13T07:29:30.911Z</t>
+  </si>
+  <si>
+    <t>Test 6: Sign A Document via Keyboard</t>
+  </si>
+  <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>14.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: locator.waitFor: Target page, context or browser has been closed
+    <t>23.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
 Call log:
-[2m  - waiting for locator('text="Add Recipients"') to be visible[22m
-Error: locator.waitFor: Target page, context or browser has been closed
+[2m  - waiting for locator('button:has-text("Prepare Document")') to be visible[22m
+TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
 Call log:
-[2m  - waiting for locator('text="Add Recipients"') to be visible[22m
-    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:270:52</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:27:06.347Z</t>
-  </si>
-  <si>
-    <t>Test 6: Sign A Document via Keyboard</t>
+[2m  - waiting for locator('button:has-text("Prepare Document")') to be visible[22m
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:461:53</t>
+  </si>
+  <si>
+    <t>2026-05-13T07:29:54.818Z</t>
+  </si>
+  <si>
+    <t>Test 7: Create Workflow from Templates via Keyboard</t>
   </si>
   <si>
     <t>SKIPPED</t>
@@ -135,19 +144,13 @@
     <t>0.00</t>
   </si>
   <si>
-    <t>2026-05-13T06:27:06.348Z</t>
-  </si>
-  <si>
-    <t>Test 7: Menu and Dropdown Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:27:06.349Z</t>
-  </si>
-  <si>
-    <t>Test 8: Combined Keyboard Workflow</t>
-  </si>
-  <si>
-    <t>2026-05-13T06:27:06.350Z</t>
+    <t>2026-05-13T07:29:54.819Z</t>
+  </si>
+  <si>
+    <t>Test 8: Use Workflow from Templates via Keyboard</t>
+  </si>
+  <si>
+    <t>2026-05-13T07:29:54.820Z</t>
   </si>
   <si>
     <t>Metric</t>
@@ -162,7 +165,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>5/13/2026, 12:27:06 PM</t>
+    <t>5/13/2026, 1:29:55 PM</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -174,7 +177,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>Failed</t>
@@ -192,25 +195,25 @@
     <t>Skipped</t>
   </si>
   <si>
-    <t>3</t>
+    <t>2</t>
   </si>
   <si>
     <t>Pass Rate</t>
   </si>
   <si>
-    <t>50.00%</t>
+    <t>62.50%</t>
   </si>
   <si>
     <t>Total Duration (s)</t>
   </si>
   <si>
-    <t>71.06</t>
+    <t>89.86</t>
   </si>
   <si>
     <t>Avg Duration (ms)</t>
   </si>
   <si>
-    <t>8882.25</t>
+    <t>11232.13</t>
   </si>
   <si>
     <t>failed</t>
@@ -749,7 +752,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>15483</v>
+        <v>14971</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>
@@ -790,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="2">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>22</v>
@@ -831,7 +834,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="2">
-        <v>17168</v>
+        <v>17398</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>25</v>
@@ -872,7 +875,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="2">
-        <v>24337</v>
+        <v>30404</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>28</v>
@@ -909,23 +912,23 @@
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3198</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E6" s="2">
-        <v>14028</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="2">
-        <v>222</v>
+        <v>309</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
@@ -934,7 +937,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>20</v>
@@ -945,28 +948,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>36</v>
+      <c r="D7" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>23823</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="2">
-        <v>287</v>
+        <v>436</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
@@ -975,7 +978,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>20</v>
@@ -986,25 +989,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="2">
-        <v>327</v>
+        <v>543</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>18</v>
@@ -1016,7 +1019,7 @@
         <v>18</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>20</v>
@@ -1027,25 +1030,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="2">
-        <v>360</v>
+        <v>652</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>18</v>
@@ -1057,7 +1060,7 @@
         <v>18</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>20</v>
@@ -1084,10 +1087,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1100,18 +1103,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1124,42 +1127,42 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1172,26 +1175,26 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1199,7 +1202,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1249,7 +1252,7 @@
         <v>9</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1257,7 +1260,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>14</v>
@@ -1266,16 +1269,16 @@
         <v>17</v>
       </c>
       <c r="E2" s="11">
-        <v>222</v>
+        <v>436</v>
       </c>
       <c r="F2" s="11">
-        <v>14028</v>
+        <v>23823</v>
       </c>
       <c r="G2" s="11">
         <v>0</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/test-results/excel-reports/stage_report_2026-05-13.xlsx
+++ b/test-results/excel-reports/stage_report_2026-05-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="63">
   <si>
     <t>No.</t>
   </si>
@@ -54,88 +54,70 @@
     <t>Environment</t>
   </si>
   <si>
-    <t>Test 1: Home Page Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>chromium &gt; ui\keyboardAccessibilityTest.stage.spec.ts &gt; ⌨️  Keyboard Navigation Suite - STAGE</t>
+    <t>Test 1: Verify home page elements</t>
+  </si>
+  <si>
+    <t>chromium &gt; ui\regressionTest.stage.spec.ts &gt; 📋 Regression Suite - STAGE Environment</t>
   </si>
   <si>
     <t>PASSED</t>
   </si>
   <si>
-    <t>14.97</t>
-  </si>
-  <si>
-    <t>tests/ui/keyboardAccessibilityTest.stage.spec.ts</t>
+    <t>15.11</t>
+  </si>
+  <si>
+    <t>tests/ui/regressionTest.stage.spec.ts</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-05-13T07:28:39.735Z</t>
+    <t>2026-05-13T08:30:15.810Z</t>
   </si>
   <si>
     <t>STAGE</t>
   </si>
   <si>
-    <t>Test 2: Landing Page Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>0.06</t>
-  </si>
-  <si>
-    <t>2026-05-13T07:28:39.825Z</t>
-  </si>
-  <si>
-    <t>Test 3: Signature Module Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>17.40</t>
-  </si>
-  <si>
-    <t>2026-05-13T07:28:57.249Z</t>
-  </si>
-  <si>
-    <t>Test 4: Upload Document via Keyboard</t>
-  </si>
-  <si>
-    <t>30.40</t>
-  </si>
-  <si>
-    <t>2026-05-13T07:29:27.679Z</t>
-  </si>
-  <si>
-    <t>Test 5: Signature Advance Workflow via Keyboard</t>
-  </si>
-  <si>
-    <t>3.20</t>
-  </si>
-  <si>
-    <t>2026-05-13T07:29:30.911Z</t>
-  </si>
-  <si>
-    <t>Test 6: Sign A Document via Keyboard</t>
+    <t>Test 2: Verify Landing Page Contents</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>2026-05-13T08:30:15.858Z</t>
+  </si>
+  <si>
+    <t>Test 3: Verify Signature Module</t>
+  </si>
+  <si>
+    <t>20.49</t>
+  </si>
+  <si>
+    <t>2026-05-13T08:30:36.364Z</t>
+  </si>
+  <si>
+    <t>Test 4: Upload Document</t>
   </si>
   <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>23.82</t>
+    <t>18.43</t>
   </si>
   <si>
     <t xml:space="preserve">TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
 Call log:
-[2m  - waiting for locator('button:has-text("Prepare Document")') to be visible[22m
+[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
 TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
 Call log:
-[2m  - waiting for locator('button:has-text("Prepare Document")') to be visible[22m
-    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:461:53</t>
-  </si>
-  <si>
-    <t>2026-05-13T07:29:54.818Z</t>
-  </si>
-  <si>
-    <t>Test 7: Create Workflow from Templates via Keyboard</t>
+[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:250:52</t>
+  </si>
+  <si>
+    <t>2026-05-13T08:30:54.872Z</t>
+  </si>
+  <si>
+    <t>Test 5: Signature Advance Workflow</t>
   </si>
   <si>
     <t>SKIPPED</t>
@@ -144,13 +126,19 @@
     <t>0.00</t>
   </si>
   <si>
-    <t>2026-05-13T07:29:54.819Z</t>
-  </si>
-  <si>
-    <t>Test 8: Use Workflow from Templates via Keyboard</t>
-  </si>
-  <si>
-    <t>2026-05-13T07:29:54.820Z</t>
+    <t>2026-05-13T08:30:54.873Z</t>
+  </si>
+  <si>
+    <t>Test 6: Sign A Document flow</t>
+  </si>
+  <si>
+    <t>Test 7: Create Workflow from Templates</t>
+  </si>
+  <si>
+    <t>Test 8: Use Workflow from Templates</t>
+  </si>
+  <si>
+    <t>2026-05-13T08:30:54.874Z</t>
   </si>
   <si>
     <t>Metric</t>
@@ -165,7 +153,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>5/13/2026, 1:29:55 PM</t>
+    <t>5/13/2026, 2:30:55 PM</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -177,7 +165,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>5</t>
+    <t>3</t>
   </si>
   <si>
     <t>Failed</t>
@@ -195,25 +183,25 @@
     <t>Skipped</t>
   </si>
   <si>
-    <t>2</t>
+    <t>4</t>
   </si>
   <si>
     <t>Pass Rate</t>
   </si>
   <si>
-    <t>62.50%</t>
+    <t>37.50%</t>
   </si>
   <si>
     <t>Total Duration (s)</t>
   </si>
   <si>
-    <t>89.86</t>
+    <t>54.07</t>
   </si>
   <si>
     <t>Avg Duration (ms)</t>
   </si>
   <si>
-    <t>11232.13</t>
+    <t>6759.13</t>
   </si>
   <si>
     <t>failed</t>
@@ -752,7 +740,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>14971</v>
+        <v>15114</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>
@@ -761,7 +749,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="2">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
@@ -793,7 +781,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="2">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>22</v>
@@ -802,7 +790,7 @@
         <v>17</v>
       </c>
       <c r="H3" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>18</v>
@@ -834,7 +822,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="2">
-        <v>17398</v>
+        <v>20487</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>25</v>
@@ -843,7 +831,7 @@
         <v>17</v>
       </c>
       <c r="H4" s="2">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>18</v>
@@ -871,23 +859,23 @@
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
+      <c r="D5" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="E5" s="2">
-        <v>30404</v>
+        <v>18435</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="2">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2">
         <v>0</v>
@@ -896,7 +884,7 @@
         <v>18</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>20</v>
@@ -907,25 +895,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>15</v>
+      <c r="D6" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="E6" s="2">
-        <v>3198</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="2">
-        <v>309</v>
+        <v>373</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>18</v>
@@ -937,7 +925,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>20</v>
@@ -948,28 +936,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="E7" s="2">
-        <v>23823</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="2">
-        <v>436</v>
+        <v>508</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
@@ -978,7 +966,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>20</v>
@@ -989,25 +977,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="2">
-        <v>543</v>
+        <v>629</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>18</v>
@@ -1019,7 +1007,7 @@
         <v>18</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>20</v>
@@ -1030,25 +1018,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="2">
-        <v>652</v>
+        <v>756</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>18</v>
@@ -1060,7 +1048,7 @@
         <v>18</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>20</v>
@@ -1087,10 +1075,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1103,18 +1091,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1127,42 +1115,42 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1175,26 +1163,26 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1202,7 +1190,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1252,7 +1240,7 @@
         <v>9</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1260,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>14</v>
@@ -1269,16 +1257,16 @@
         <v>17</v>
       </c>
       <c r="E2" s="11">
-        <v>436</v>
+        <v>214</v>
       </c>
       <c r="F2" s="11">
-        <v>23823</v>
+        <v>18435</v>
       </c>
       <c r="G2" s="11">
         <v>0</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/test-results/excel-reports/stage_report_2026-05-13.xlsx
+++ b/test-results/excel-reports/stage_report_2026-05-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
   <si>
     <t>No.</t>
   </si>
@@ -60,19 +60,28 @@
     <t>chromium &gt; ui\regressionTest.stage.spec.ts &gt; 📋 Regression Suite - STAGE Environment</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>15.11</t>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>35.66</t>
   </si>
   <si>
     <t>tests/ui/regressionTest.stage.spec.ts</t>
   </si>
   <si>
+    <t xml:space="preserve">Error: page.goto: Target page, context or browser has been closed
+Call log:
+[2m  - navigating to "https://app.selisestage.com/login", waiting until "load"[22m
+Error: page.goto: Target page, context or browser has been closed
+Call log:
+[2m  - navigating to "https://app.selisestage.com/login", waiting until "load"[22m
+    at Object.page (C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\src\pages\basePage.ts:151:24)</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>2026-05-13T08:30:15.810Z</t>
+    <t>2026-05-13T09:55:38.378Z</t>
   </si>
   <si>
     <t>STAGE</t>
@@ -81,52 +90,28 @@
     <t>Test 2: Verify Landing Page Contents</t>
   </si>
   <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>2026-05-13T08:30:15.858Z</t>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>2026-05-13T09:55:38.380Z</t>
   </si>
   <si>
     <t>Test 3: Verify Signature Module</t>
   </si>
   <si>
-    <t>20.49</t>
-  </si>
-  <si>
-    <t>2026-05-13T08:30:36.364Z</t>
+    <t>2026-05-13T09:55:38.381Z</t>
   </si>
   <si>
     <t>Test 4: Upload Document</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>18.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
-Call log:
-[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
-TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
-Call log:
-[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
-    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:250:52</t>
-  </si>
-  <si>
-    <t>2026-05-13T08:30:54.872Z</t>
-  </si>
-  <si>
     <t>Test 5: Signature Advance Workflow</t>
   </si>
   <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>0.00</t>
-  </si>
-  <si>
-    <t>2026-05-13T08:30:54.873Z</t>
+    <t>2026-05-13T09:55:38.382Z</t>
   </si>
   <si>
     <t>Test 6: Sign A Document flow</t>
@@ -138,9 +123,6 @@
     <t>Test 8: Use Workflow from Templates</t>
   </si>
   <si>
-    <t>2026-05-13T08:30:54.874Z</t>
-  </si>
-  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -153,7 +135,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>5/13/2026, 2:30:55 PM</t>
+    <t>5/13/2026, 3:55:38 PM</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -165,7 +147,7 @@
     <t>Passed</t>
   </si>
   <si>
-    <t>3</t>
+    <t>0</t>
   </si>
   <si>
     <t>Failed</t>
@@ -177,31 +159,25 @@
     <t>Timed Out</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Skipped</t>
   </si>
   <si>
-    <t>4</t>
+    <t>7</t>
   </si>
   <si>
     <t>Pass Rate</t>
   </si>
   <si>
-    <t>37.50%</t>
+    <t>0.00%</t>
   </si>
   <si>
     <t>Total Duration (s)</t>
   </si>
   <si>
-    <t>54.07</t>
-  </si>
-  <si>
     <t>Avg Duration (ms)</t>
   </si>
   <si>
-    <t>6759.13</t>
+    <t>4458.13</t>
   </si>
   <si>
     <t>failed</t>
@@ -214,7 +190,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -229,10 +205,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF006100"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF9C0006"/>
     </font>
     <font>
@@ -243,7 +215,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,11 +225,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -300,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -314,14 +281,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -740,7 +704,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>15114</v>
+        <v>35665</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>
@@ -758,13 +722,13 @@
         <v>0</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -772,19 +736,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E3" s="2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
@@ -793,19 +757,19 @@
         <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -813,19 +777,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
+      <c r="D4" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E4" s="2">
-        <v>20487</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -834,19 +798,19 @@
         <v>129</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -854,19 +818,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2">
-        <v>18435</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>17</v>
@@ -875,19 +839,19 @@
         <v>214</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2">
         <v>0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -895,19 +859,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>33</v>
+      <c r="D6" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
@@ -916,19 +880,19 @@
         <v>373</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -936,19 +900,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>33</v>
+      <c r="D7" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
@@ -957,19 +921,19 @@
         <v>508</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -977,19 +941,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
+      <c r="D8" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -998,19 +962,19 @@
         <v>629</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1018,19 +982,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
+      <c r="D9" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>17</v>
@@ -1039,19 +1003,19 @@
         <v>756</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1073,124 +1037,124 @@
     <col min="2" max="2" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="6" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="8" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="8" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="B10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="8" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="B13" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1217,56 +1181,56 @@
     <col min="8" max="8" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>62</v>
+      <c r="H1" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="11">
-        <v>214</v>
-      </c>
-      <c r="F2" s="11">
-        <v>18435</v>
-      </c>
-      <c r="G2" s="11">
-        <v>0</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>30</v>
+      <c r="E2" s="10">
+        <v>77</v>
+      </c>
+      <c r="F2" s="10">
+        <v>35665</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/test-results/excel-reports/stage_report_2026-05-13.xlsx
+++ b/test-results/excel-reports/stage_report_2026-05-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="46">
   <si>
     <t>No.</t>
   </si>
@@ -54,66 +54,40 @@
     <t>Environment</t>
   </si>
   <si>
-    <t>Test 1: Verify home page elements</t>
+    <t>Test 7: Create Workflow from Templates</t>
   </si>
   <si>
     <t>chromium &gt; ui\regressionTest.stage.spec.ts &gt; 📋 Regression Suite - STAGE Environment</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>23.24</t>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>42.66</t>
   </si>
   <si>
     <t>tests/ui/regressionTest.stage.spec.ts</t>
   </si>
   <si>
+    <t xml:space="preserve">TimeoutError: locator.waitFor: Timeout 15000ms exceeded.
+Call log:
+[2m  - waiting for locator('button.create-template-btn:visible').first() to be visible[22m
+TimeoutError: locator.waitFor: Timeout 15000ms exceeded.
+Call log:
+[2m  - waiting for locator('button.create-template-btn:visible').first() to be visible[22m
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:649:29</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>2026-05-13T11:45:06.507Z</t>
+    <t>2026-05-13T11:59:32.822Z</t>
   </si>
   <si>
     <t>STAGE</t>
   </si>
   <si>
-    <t>Test 2: Verify Landing Page Contents</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>2026-05-13T11:45:06.557Z</t>
-  </si>
-  <si>
-    <t>Test 3: Verify Signature Module</t>
-  </si>
-  <si>
-    <t>29.15</t>
-  </si>
-  <si>
-    <t>2026-05-13T11:45:35.721Z</t>
-  </si>
-  <si>
-    <t>Test 4: Upload Document</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>14.87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: page.waitForTimeout: Target page, context or browser has been closed
-Error: page.waitForTimeout: Target page, context or browser has been closed
-    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:246:16</t>
-  </si>
-  <si>
-    <t>2026-05-13T11:45:50.670Z</t>
-  </si>
-  <si>
-    <t>Test 5: Signature Advance Workflow</t>
+    <t>Test 8: Use Workflow from Templates</t>
   </si>
   <si>
     <t>SKIPPED</t>
@@ -122,19 +96,7 @@
     <t>0.00</t>
   </si>
   <si>
-    <t>2026-05-13T11:45:50.671Z</t>
-  </si>
-  <si>
-    <t>Test 6: Sign A Document flow</t>
-  </si>
-  <si>
-    <t>2026-05-13T11:45:50.672Z</t>
-  </si>
-  <si>
-    <t>Test 7: Create Workflow from Templates</t>
-  </si>
-  <si>
-    <t>Test 8: Use Workflow from Templates</t>
+    <t>2026-05-13T11:59:32.823Z</t>
   </si>
   <si>
     <t>Metric</t>
@@ -149,19 +111,19 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>5/13/2026, 5:45:51 PM</t>
+    <t>5/13/2026, 5:59:33 PM</t>
   </si>
   <si>
     <t>Total Tests</t>
   </si>
   <si>
-    <t>8</t>
+    <t>2</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>3</t>
+    <t>0</t>
   </si>
   <si>
     <t>Failed</t>
@@ -173,31 +135,22 @@
     <t>Timed Out</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Skipped</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Pass Rate</t>
   </si>
   <si>
-    <t>37.50%</t>
+    <t>0.00%</t>
   </si>
   <si>
     <t>Total Duration (s)</t>
   </si>
   <si>
-    <t>67.30</t>
-  </si>
-  <si>
     <t>Avg Duration (ms)</t>
   </si>
   <si>
-    <t>8413.00</t>
+    <t>21328.50</t>
   </si>
   <si>
     <t>failed</t>
@@ -210,7 +163,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -225,10 +178,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF006100"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF9C0006"/>
     </font>
     <font>
@@ -239,7 +188,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,11 +198,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -296,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -310,14 +254,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -663,7 +604,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -736,7 +677,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>23238</v>
+        <v>42657</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>
@@ -745,7 +686,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="2">
-        <v>77</v>
+        <v>629</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
@@ -754,13 +695,13 @@
         <v>0</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -768,286 +709,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E3" s="2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="2">
-        <v>91</v>
+        <v>756</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2">
-        <v>29153</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="2">
-        <v>129</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="2">
-        <v>14872</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="2">
-        <v>214</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="2">
-        <v>373</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="2">
-        <v>508</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="2">
-        <v>629</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="2">
-        <v>756</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1069,124 +764,124 @@
     <col min="2" max="2" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="6" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B13" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="8" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1213,56 +908,56 @@
     <col min="8" max="8" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>62</v>
+      <c r="H1" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="11">
-        <v>214</v>
-      </c>
-      <c r="F2" s="11">
-        <v>14872</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="E2" s="10">
+        <v>629</v>
+      </c>
+      <c r="F2" s="10">
+        <v>42657</v>
+      </c>
+      <c r="G2" s="10">
         <v>0</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>30</v>
+      <c r="H2" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
